--- a/문서/contents.xlsx
+++ b/문서/contents.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="570" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="560" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>idx</t>
   </si>
@@ -48,6 +48,72 @@
   </si>
   <si>
     <t>jp</t>
+  </si>
+  <si>
+    <t>확인</t>
+  </si>
+  <si>
+    <t>취소</t>
+  </si>
+  <si>
+    <t>메인 메뉴로\n나가시겠습니까?</t>
+  </si>
+  <si>
+    <t>Go to</t>
+  </si>
+  <si>
+    <t>Go to\nMainMenu?</t>
+  </si>
+  <si>
+    <t>Confirm</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>그만두기</t>
+  </si>
+  <si>
+    <t>Quit</t>
+  </si>
+  <si>
+    <t>숏 소드</t>
+  </si>
+  <si>
+    <t>Sword</t>
+  </si>
+  <si>
+    <t>소드</t>
+  </si>
+  <si>
+    <t>배경음</t>
+  </si>
+  <si>
+    <t>VOL</t>
+  </si>
+  <si>
+    <t>FX</t>
+  </si>
+  <si>
+    <t>효과</t>
+  </si>
+  <si>
+    <t>언어</t>
+  </si>
+  <si>
+    <t>한국어</t>
+  </si>
+  <si>
+    <t>영어</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Korean</t>
+  </si>
+  <si>
+    <t>Language</t>
   </si>
 </sst>
 </file>
@@ -599,12 +665,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -924,12 +993,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="1" width="14.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="2" max="3" width="40.63000107" customWidth="1" outlineLevel="0"/>
-    <col min="4" max="4" width="38.38000107" customWidth="1" outlineLevel="0"/>
+    <col min="1" max="1" style="1" width="14.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="3" style="1" width="40.63000107" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="4" style="1" width="38.38000107" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -978,64 +1047,127 @@
       <c r="A4" s="1">
         <v>10002</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1">
         <v>10003</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1">
         <v>10004</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1">
         <v>10005</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1">
         <v>10006</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1">
         <v>10007</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1">
         <v>10008</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1">
         <v>10009</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1">
         <v>10010</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1">
@@ -1043,6 +1175,7 @@
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1">
@@ -1050,6 +1183,7 @@
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1">
@@ -1057,6 +1191,7 @@
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1">
@@ -1064,6 +1199,189 @@
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1">
+        <v>20001</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
